--- a/giro_da_praça_ofertas - quarta.xlsx
+++ b/giro_da_praça_ofertas - quarta.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,24 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -59,7 +77,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0045A045"/>
+        <bgColor rgb="0045A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,24 +115,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -476,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -522,7 +558,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+          <t>QUARTA - OFERTA ESPECIAL 03/12/25</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -531,1397 +567,1397 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
+        <v>100038</v>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="5" t="n">
+        <v>22.99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
         <v>273799</v>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>ARROZ DELLARROZ PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr"/>
-      <c r="F2" s="6" t="n">
+      <c r="E3" s="9" t="inlineStr"/>
+      <c r="F3" s="10" t="n">
         <v>21.99</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C4" s="7" t="n">
         <v>325990</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>ARROZ FLORA PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="6" t="n">
+      <c r="E4" s="9" t="inlineStr"/>
+      <c r="F4" s="10" t="n">
         <v>18.99</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C5" s="7" t="n">
         <v>225003</v>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>ARROZ RAMPINELLI PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="6" t="n">
+      <c r="E5" s="9" t="inlineStr"/>
+      <c r="F5" s="10" t="n">
         <v>21.99</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 AÇÚCAR E ADOÇANTES</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C6" s="7" t="n">
         <v>298239</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>AÇÚCAR CRISTAL ECOÇUCAR 2KG</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="6" t="n">
+      <c r="E6" s="9" t="inlineStr"/>
+      <c r="F6" s="10" t="n">
         <v>6.99</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 FEIJÕES E LEGUMINOSAS</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C7" s="7" t="n">
         <v>279573</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>FEIJÃO CARIOCA DONA MARIA 1KG</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="6" t="n">
+      <c r="E7" s="9" t="inlineStr"/>
+      <c r="F7" s="10" t="n">
         <v>5.59</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 FEIJÕES E LEGUMINOSAS</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C8" s="7" t="n">
         <v>327443</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>FEIJÃO CARIOCA KALDINHO 1KG</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="6" t="n">
+      <c r="E8" s="9" t="inlineStr"/>
+      <c r="F8" s="10" t="n">
         <v>5.19</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 ÓLEOS E GORDURAS</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C9" s="7" t="n">
         <v>106680</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>ÓLEO DE SOJA SOYA 900ML</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="6" t="n">
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="10" t="n">
         <v>8.49</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-    </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C11" s="7" t="n">
         <v>255232</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="6" t="n">
+      <c r="E11" s="9" t="inlineStr"/>
+      <c r="F11" s="10" t="n">
         <v>19.49</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C12" s="7" t="n">
         <v>101137</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>CAFÉ MARATA 250G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="6" t="n">
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="10" t="n">
         <v>15.99</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C13" s="7" t="n">
         <v>101136</v>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>CAFÉ PILÃO 250G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="6" t="n">
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="10" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C14" s="7" t="n">
         <v>186826</v>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>BISCOITO CREAM CRACKER GALLO 360G</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="6" t="n">
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="10" t="n">
         <v>5.39</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="7" t="n">
         <v>286197</v>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>BISCOITO ROSQUINHA MABEL 600G COCO</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="6" t="n">
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="10" t="n">
         <v>8.59</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C16" s="7" t="n">
         <v>273714</v>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="6" t="n">
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="10" t="n">
         <v>7.99</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C17" s="7" t="n">
         <v>100789</v>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>KETCHUP QUERO 400G</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>PICANTE, TRADICIONAL</t>
         </is>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F17" s="10" t="n">
         <v>8.390000000000001</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C18" s="7" t="n">
         <v>101728</v>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>MAIONESE HELLMANNS 500G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="6" t="n">
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="10" t="n">
         <v>13.39</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C19" s="7" t="n">
         <v>286586</v>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>MOLHO DE TOMATE SOFRUTA 300G PIZZA</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="6" t="n">
+      <c r="E19" s="9" t="inlineStr"/>
+      <c r="F19" s="10" t="n">
         <v>2.89</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C20" s="7" t="n">
         <v>106831</v>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>TEMPERO COMPLETO SABORELLE 930G</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>COM PIMENTA, SEM PIMENTA</t>
         </is>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F20" s="10" t="n">
         <v>12.99</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C21" s="7" t="n">
         <v>100884</v>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>TEMPERO EM PÓ SAZON SACHÊ 60G CARNES/VERMELHO</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="6" t="n">
+      <c r="E21" s="9" t="inlineStr"/>
+      <c r="F21" s="10" t="n">
         <v>5.99</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C22" s="7" t="n">
         <v>106961</v>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>VINAGRE CASTELO 750ML</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>ALCOOL, ALCOOL COLORIDO</t>
         </is>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F22" s="10" t="n">
         <v>3.99</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONSERVAS - HORTIFRUTI</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C23" s="7" t="n">
         <v>234316</v>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>MILHO VERDE SOFRUTA LATA 170G</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="6" t="n">
+      <c r="E23" s="9" t="inlineStr"/>
+      <c r="F23" s="10" t="n">
         <v>3.99</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C24" s="7" t="n">
         <v>112978</v>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>CUSCUZ DE MILHO SINHA 500G</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="6" t="n">
+      <c r="E24" s="9" t="inlineStr"/>
+      <c r="F24" s="10" t="n">
         <v>2.79</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C25" s="7" t="n">
         <v>100027</v>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>FARINHA DE TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="6" t="n">
+      <c r="E25" s="9" t="inlineStr"/>
+      <c r="F25" s="10" t="n">
         <v>7.99</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C26" s="7" t="n">
         <v>273006</v>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>FARINHA LACTEA NESTLÉ 160G ORIGINAL</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="6" t="n">
+      <c r="E26" s="9" t="inlineStr"/>
+      <c r="F26" s="10" t="n">
         <v>6.99</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C27" s="7" t="n">
         <v>294705</v>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>FLOCÃO DE ARROZ JALAPÃO 400G</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="6" t="n">
+      <c r="E27" s="9" t="inlineStr"/>
+      <c r="F27" s="10" t="n">
         <v>2.29</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="C28" s="7" t="n">
         <v>100119</v>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>FLOCÃO DE MILHO SINHA 500G</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="6" t="n">
+      <c r="E28" s="9" t="inlineStr"/>
+      <c r="F28" s="10" t="n">
         <v>2.99</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C29" s="7" t="n">
         <v>149122</v>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>MASSA PARA TAPIOCA AMAFIL 1KG</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="6" t="n">
+      <c r="E29" s="9" t="inlineStr"/>
+      <c r="F29" s="10" t="n">
         <v>6.99</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C30" s="7" t="n">
         <v>145874</v>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>POLVILHO MATUTO 1KG AZEDO</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="6" t="n">
+      <c r="E30" s="9" t="inlineStr"/>
+      <c r="F30" s="10" t="n">
         <v>10.99</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C31" s="7" t="n">
         <v>128920</v>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>POLVILHO MATUTO 1KG DOCE</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="6" t="n">
+      <c r="E31" s="9" t="inlineStr"/>
+      <c r="F31" s="10" t="n">
         <v>7.69</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C32" s="7" t="n">
         <v>101874</v>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>TODDYNHO 200ML CHOCOLATE</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="6" t="n">
+      <c r="E32" s="9" t="inlineStr"/>
+      <c r="F32" s="10" t="n">
         <v>2.79</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C33" s="7" t="n">
         <v>101063</v>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>CREME DE LEITE PIRACANJUBA 200G</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="6" t="n">
+      <c r="E33" s="9" t="inlineStr"/>
+      <c r="F33" s="10" t="n">
         <v>3.39</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C34" s="7" t="n">
         <v>101083</v>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>LEITE CONDENSADO PIRACANJUBA 395G</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="6" t="n">
+      <c r="E34" s="9" t="inlineStr"/>
+      <c r="F34" s="10" t="n">
         <v>7.19</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C35" s="7" t="n">
         <v>142446</v>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>LEITE LONGA VIDA ITALAC 1L INTEGRAL</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="6" t="n">
+      <c r="E35" s="9" t="inlineStr"/>
+      <c r="F35" s="10" t="n">
         <v>6.39</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="C36" s="7" t="n">
         <v>219003</v>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LEITE LONGA VIDA ITALAC 1L INTEGRAL ZERO LACTOSE </t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="6" t="n">
+      <c r="E36" s="9" t="inlineStr"/>
+      <c r="F36" s="10" t="n">
         <v>6.99</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE EM PÓ</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="C37" s="7" t="n">
         <v>106922</v>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>LEITE EM PÓ CCGL 1KG INTEGRAL</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="6" t="n">
+      <c r="E37" s="9" t="inlineStr"/>
+      <c r="F37" s="10" t="n">
         <v>41.99</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C38" s="7" t="n">
         <v>303196</v>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>MACARRÃO GALO 400G ESPAGUETE AMARELO</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="6" t="n">
+      <c r="E38" s="9" t="inlineStr"/>
+      <c r="F38" s="10" t="n">
         <v>3.39</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - MASSAS</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C39" s="7" t="n">
         <v>142475</v>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>MACARRÃO PAULISTA 500G PARAFUSO COM OVOS</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="6" t="n">
+      <c r="E39" s="9" t="inlineStr"/>
+      <c r="F39" s="10" t="n">
         <v>3.19</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-    </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>#03 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="C41" s="7" t="n">
         <v>100431</v>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>ÁGUA SANITÁRIA QBOA 2L</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="6" t="n">
+      <c r="E41" s="9" t="inlineStr"/>
+      <c r="F41" s="10" t="n">
         <v>7.19</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>#03 LIMPEZA - AMACIANTES</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="C42" s="7" t="n">
         <v>116139</v>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>AMACIANTE DE ROUPAS +FAMILIA 2L FLORISTA</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="6" t="n">
+      <c r="E42" s="9" t="inlineStr"/>
+      <c r="F42" s="10" t="n">
         <v>7.59</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>#03 LIMPEZA - DESINFETANTES</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C43" s="7" t="n">
         <v>142863</v>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>DESINFETANTE YPÊ BAK 2L</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>EUCALIPTO, FLORAL, LAVANDA</t>
         </is>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F43" s="10" t="n">
         <v>12.99</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>#03 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="C44" s="7" t="n">
         <v>100391</v>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>DETERGENTE LIQUIDO YPÊ 500ML</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>CAPIM LIMÃO, CLEAR, CLEAR CARE, COCO, LIMAO, MACA, NEUTRO</t>
         </is>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F44" s="10" t="n">
         <v>2.79</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>#03 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="C45" s="7" t="n">
         <v>257710</v>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>SABÃO EM BARRA YPÊ 900G NEUTRO</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="6" t="n">
+      <c r="E45" s="9" t="inlineStr"/>
+      <c r="F45" s="10" t="n">
         <v>12.49</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>#03 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="C46" s="7" t="n">
         <v>261980</v>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>SABÃO EM PÓ BRILHANTE CAIXA 1,6KG LIMPEZA TOTAL</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr"/>
-      <c r="F45" s="6" t="n">
+      <c r="E46" s="9" t="inlineStr"/>
+      <c r="F46" s="10" t="n">
         <v>19.99</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>#03 LIMPEZA - SABÃO</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="C47" s="7" t="n">
         <v>228234</v>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>SABÃO EM PÓ OMO CAIXA 800G LAVAGEM PERFEITA</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="6" t="n">
+      <c r="E47" s="9" t="inlineStr"/>
+      <c r="F47" s="10" t="n">
         <v>14.99</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>#03 LIMPEZA - SODAS</t>
         </is>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="C48" s="7" t="n">
         <v>100373</v>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>SODA CAUSTICA SOL 1KG</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="6" t="n">
+      <c r="E48" s="9" t="inlineStr"/>
+      <c r="F48" s="10" t="n">
         <v>25.99</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-    </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>#04 HIGIENE PESSOAL - CABELOS</t>
         </is>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="C50" s="7" t="n">
         <v>259776</v>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>MÁSCARA CAPILAR CAVALO FORTE HASKELL 900G</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr"/>
-      <c r="F49" s="6" t="n">
+      <c r="E50" s="9" t="inlineStr"/>
+      <c r="F50" s="10" t="n">
         <v>69.98999999999999</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>#04 HIGIENE PESSOAL - PAPEL HIGIENICO</t>
         </is>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="C51" s="7" t="n">
         <v>316605</v>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>PAPEL HIGIENICO CAPRICE 12X20M NEUTRO FOLHA DUPLA</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="6" t="n">
+      <c r="E51" s="9" t="inlineStr"/>
+      <c r="F51" s="10" t="n">
         <v>13.99</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-    </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="C53" s="7" t="n">
         <v>104406</v>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="6" t="n">
+      <c r="E53" s="9" t="inlineStr"/>
+      <c r="F53" s="10" t="n">
         <v>10.49</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="C54" s="7" t="n">
         <v>104410</v>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>REFRIGERANTE GUARANA ANTARCTICA 2L</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr"/>
-      <c r="F53" s="6" t="n">
+      <c r="E54" s="9" t="inlineStr"/>
+      <c r="F54" s="10" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
         </is>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="C55" s="7" t="n">
         <v>104424</v>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>REFRIGERANTE PEPSI 2L COLA</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr"/>
-      <c r="F54" s="6" t="n">
+      <c r="E55" s="9" t="inlineStr"/>
+      <c r="F55" s="10" t="n">
         <v>7.99</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
         </is>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="C56" s="7" t="n">
         <v>286325</v>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>SUCO AURORA TP 1,5L UVA TINTO</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="6" t="n">
+      <c r="E56" s="9" t="inlineStr"/>
+      <c r="F56" s="10" t="n">
         <v>21.99</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="C57" s="7" t="n">
         <v>242930</v>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>CERVEJA HEINEKEN 330ML</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="6" t="n">
+      <c r="E57" s="9" t="inlineStr"/>
+      <c r="F57" s="10" t="n">
         <v>6.89</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="C58" s="7" t="n">
         <v>239446</v>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>CERVEJA AMSTEL 12 X 269ML LAGER</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr"/>
-      <c r="F57" s="6" t="n">
+      <c r="E58" s="9" t="inlineStr"/>
+      <c r="F58" s="10" t="n">
         <v>3.06</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="C59" s="7" t="n">
         <v>168712</v>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>CERVEJA ANTARCTICA 15 X 269ML PILSEN</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="6" t="n">
+      <c r="E59" s="9" t="inlineStr"/>
+      <c r="F59" s="10" t="n">
         <v>3.29</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="C60" s="7" t="n">
         <v>170451</v>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA BRAHMA 15 X 269ML CHOPP </t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr"/>
-      <c r="F59" s="6" t="n">
+      <c r="E60" s="9" t="inlineStr"/>
+      <c r="F60" s="10" t="n">
         <v>3.15</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>SEGUNDA/QUARTA - OFERTAS 01 A 03/12/25</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="C61" s="7" t="n">
         <v>102085</v>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>CACHAÇA 51 965ML</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr"/>
-      <c r="F60" s="6" t="n">
+      <c r="E61" s="9" t="inlineStr"/>
+      <c r="F61" s="10" t="n">
         <v>12.99</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-    </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 03/12/25</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>158997</v>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>BISTECA BOVINA DO ACÉM KG</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr"/>
-      <c r="F62" s="6" t="n">
-        <v>16.99</v>
-      </c>
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1931,20 +1967,20 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>105457</v>
+        <v>119927</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>CARNE BOVINA SERENADA KG</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr"/>
-      <c r="F63" s="6" t="n">
-        <v>33.99</v>
+          <t xml:space="preserve">FRANGO AMERICANO KG CONGELADO </t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="5" t="n">
+        <v>10.99</v>
       </c>
     </row>
     <row r="64">
@@ -1955,364 +1991,364 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>336782</v>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>FRANGO FERREIRA KG CONGELADO COM MIUDOS</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="5" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 03/12/25</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C64" s="3" t="n">
+      <c r="C65" s="7" t="n">
+        <v>158997</v>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>BISTECA BOVINA DO ACÉM KG</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr"/>
+      <c r="F65" s="10" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 03/12/25</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>105457</v>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>CARNE BOVINA SERENADA KG</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr"/>
+      <c r="F66" s="10" t="n">
+        <v>33.99</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 03/12/25</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="n">
         <v>105456</v>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>CARNE DE SOL KG SEGUNDA</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr"/>
-      <c r="F64" s="6" t="n">
+      <c r="E67" s="9" t="inlineStr"/>
+      <c r="F67" s="10" t="n">
         <v>28.99</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>QUARTA - AÇOUGUE 03/12/25</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C65" s="3" t="n">
+      <c r="C68" s="7" t="n">
         <v>105468</v>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D68" s="8" t="inlineStr">
         <is>
           <t>CARNE MOIDA KG</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr"/>
-      <c r="F65" s="6" t="n">
+      <c r="E68" s="9" t="inlineStr"/>
+      <c r="F68" s="10" t="n">
         <v>18.99</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>QUARTA - AÇOUGUE 03/12/25</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C66" s="3" t="n">
+      <c r="C69" s="7" t="n">
         <v>105471</v>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>COSTELA BOVINA KG</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr"/>
-      <c r="F66" s="6" t="n">
+      <c r="E69" s="9" t="inlineStr"/>
+      <c r="F69" s="10" t="n">
         <v>16.99</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>QUARTA - AÇOUGUE 03/12/25</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C67" s="3" t="n">
+      <c r="C70" s="7" t="n">
         <v>105435</v>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>COXÃO MOLE KG</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr"/>
-      <c r="F67" s="6" t="n">
+      <c r="E70" s="9" t="inlineStr"/>
+      <c r="F70" s="10" t="n">
         <v>38.99</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>QUARTA - AÇOUGUE 03/12/25</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C68" s="3" t="n">
+      <c r="C71" s="7" t="n">
         <v>105474</v>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>FRALDINHA BOVINA KG</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr"/>
-      <c r="F68" s="6" t="n">
+      <c r="E71" s="9" t="inlineStr"/>
+      <c r="F71" s="10" t="n">
         <v>32.99</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>QUARTA - AÇOUGUE 03/12/25</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C69" s="3" t="n">
+      <c r="C72" s="7" t="n">
         <v>298422</v>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D72" s="8" t="inlineStr">
         <is>
           <t>SUINO CAIPIRA KG</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr"/>
-      <c r="F69" s="6" t="n">
+      <c r="E72" s="9" t="inlineStr"/>
+      <c r="F72" s="10" t="n">
         <v>21.99</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>QUARTA - AÇOUGUE 03/12/25</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C70" s="3" t="n">
+      <c r="C73" s="7" t="n">
         <v>105062</v>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>BISTECA SUINA DO PERNIL KG</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr"/>
-      <c r="F70" s="6" t="n">
+      <c r="E73" s="9" t="inlineStr"/>
+      <c r="F73" s="10" t="n">
         <v>17.99</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>QUARTA - AÇOUGUE 03/12/25</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C71" s="3" t="n">
+      <c r="C74" s="7" t="n">
         <v>106008</v>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D74" s="8" t="inlineStr">
         <is>
           <t>INGREDIENTES PARA FEIJOADA KG</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr"/>
-      <c r="F71" s="6" t="n">
+      <c r="E74" s="9" t="inlineStr"/>
+      <c r="F74" s="10" t="n">
         <v>16.99</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>QUARTA - AÇOUGUE 03/12/25</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C72" s="3" t="n">
+      <c r="C75" s="7" t="n">
         <v>106034</v>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>SUAN SUINA KG</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr"/>
-      <c r="F72" s="6" t="n">
+      <c r="E75" s="9" t="inlineStr"/>
+      <c r="F75" s="10" t="n">
         <v>10.99</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>QUARTA - AÇOUGUE 03/12/25</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C73" s="3" t="n">
+      <c r="C76" s="7" t="n">
         <v>305039</v>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>LINGUIÇA CASEIRA BOVINA KG</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr"/>
-      <c r="F73" s="6" t="n">
+      <c r="E76" s="9" t="inlineStr"/>
+      <c r="F76" s="10" t="n">
         <v>16.99</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>QUARTA - VERDURA 03/12/25</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C75" s="3" t="n">
+      <c r="C78" s="7" t="n">
         <v>105023</v>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>BANANA PRATA KG</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr"/>
-      <c r="F75" s="6" t="n">
+      <c r="E78" s="9" t="inlineStr"/>
+      <c r="F78" s="10" t="n">
         <v>5.99</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>QUARTA - VERDURA 03/12/25</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
-      <c r="C76" s="3" t="n">
+      <c r="C79" s="7" t="n">
         <v>104931</v>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>LARANJA KG</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr"/>
-      <c r="F76" s="6" t="n">
+      <c r="E79" s="9" t="inlineStr"/>
+      <c r="F79" s="10" t="n">
         <v>6.99</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 03/12/25</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="n">
-        <v>104928</v>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>MANGA KG PALMER</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr"/>
-      <c r="F77" s="6" t="n">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 03/12/25</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="n">
-        <v>104883</v>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>MANGA KG TOMY</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr"/>
-      <c r="F78" s="6" t="n">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 03/12/25</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - FRUTAS</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="n">
-        <v>104944</v>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>MAÇÃ NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr"/>
-      <c r="F79" s="6" t="n">
-        <v>11.99</v>
       </c>
     </row>
     <row r="80">
@@ -2327,16 +2363,16 @@
         </is>
       </c>
       <c r="C80" s="3" t="n">
-        <v>104947</v>
+        <v>104928</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>MELANCIA INTEIRA KG</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr"/>
-      <c r="F80" s="6" t="n">
-        <v>2.39</v>
+          <t>MANGA KG PALMER</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="5" t="n">
+        <v>5.59</v>
       </c>
     </row>
     <row r="81">
@@ -2351,16 +2387,16 @@
         </is>
       </c>
       <c r="C81" s="3" t="n">
-        <v>104996</v>
+        <v>104883</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>MELÃO AMARELO KG</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr"/>
-      <c r="F81" s="6" t="n">
-        <v>5.99</v>
+          <t>MANGA KG TOMY</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="5" t="n">
+        <v>5.59</v>
       </c>
     </row>
     <row r="82">
@@ -2371,68 +2407,68 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
-        <v>105010</v>
+        <v>104944</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>BATATA MONALISA KG</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr"/>
-      <c r="F82" s="6" t="n">
-        <v>4.99</v>
+          <t>MAÇÃ NACIONAL KG</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="5" t="n">
+        <v>12.99</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>QUARTA - VERDURA 03/12/25</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="n">
-        <v>105001</v>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>BETERRABA KG</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr"/>
-      <c r="F83" s="6" t="n">
-        <v>4.99</v>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>104947</v>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>MELANCIA INTEIRA KG</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr"/>
+      <c r="F83" s="10" t="n">
+        <v>2.39</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>QUARTA - VERDURA 03/12/25</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="n">
-        <v>104862</v>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>CENOURA KG</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr"/>
-      <c r="F84" s="6" t="n">
-        <v>3.99</v>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - FRUTAS</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>104996</v>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>MELÃO AMARELO KG</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr"/>
+      <c r="F84" s="10" t="n">
+        <v>5.99</v>
       </c>
     </row>
     <row r="85">
@@ -2447,16 +2483,16 @@
         </is>
       </c>
       <c r="C85" s="3" t="n">
-        <v>104961</v>
+        <v>105010</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>TOMATE CARMEM KG</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr"/>
-      <c r="F85" s="6" t="n">
-        <v>5.99</v>
+          <t>BATATA MONALISA KG</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="5" t="n">
+        <v>4.19</v>
       </c>
     </row>
     <row r="86">
@@ -2471,40 +2507,40 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>104863</v>
+        <v>105001</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>TOMATE SALADETE KG</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr"/>
-      <c r="F86" s="6" t="n">
-        <v>6.19</v>
+          <t>BETERRABA KG</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="5" t="n">
+        <v>3.99</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>QUARTA - VERDURA 03/12/25</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="n">
-        <v>104937</v>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>ALHO A GRANEL KG</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr"/>
-      <c r="F87" s="6" t="n">
-        <v>24.99</v>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>104862</v>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>CENOURA KG</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr"/>
+      <c r="F87" s="10" t="n">
+        <v>3.99</v>
       </c>
     </row>
     <row r="88">
@@ -2515,20 +2551,20 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
-        <v>104919</v>
+        <v>104961</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>CEBOLA NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr"/>
-      <c r="F88" s="6" t="n">
-        <v>1.99</v>
+          <t>TOMATE CARMEM KG</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="5" t="n">
+        <v>4.99</v>
       </c>
     </row>
     <row r="89">
@@ -2539,20 +2575,204 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
+          <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>104863</v>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>TOMATE SALADETE KG</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="5" t="n">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 03/12/25</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="n">
+        <v>104937</v>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>ALHO A GRANEL KG</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr"/>
+      <c r="F90" s="10" t="n">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 03/12/25</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI - TEMPEROS FRESCOS</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="n">
+        <v>104919</v>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>CEBOLA NACIONAL KG</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr"/>
+      <c r="F91" s="10" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 03/12/25</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
           <t>#09 HORTIFRUTI - VERDURAS E FOLHAGENS</t>
         </is>
       </c>
-      <c r="C89" s="3" t="n">
+      <c r="C92" s="7" t="n">
         <v>104992</v>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D92" s="8" t="inlineStr">
         <is>
           <t>REPOLHO VERDE KG</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr"/>
-      <c r="F89" s="6" t="n">
+      <c r="E92" s="9" t="inlineStr"/>
+      <c r="F92" s="10" t="n">
         <v>2.79</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 03/12/25</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>#10 OVOS</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>337347</v>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>OVOS DE GRANJA EMAPE BDJ 20UN BRANCOS GRANDES</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="5" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 03/12/25</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>#10 OVOS</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>337345</v>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>OVOS DE GRANJA EMAPE BDJ 30UN BRANCOS GRANDES</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="5" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 03/12/25</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>#10 OVOS</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>331438</v>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>OVOS DE GRANJA IANA BDJ 20UN</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>BRANCOS</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 03/12/25</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>#10 OVOS</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>328966</v>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>OVOS DE GRANJA IANA BDJ 30UN</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>BRANCOS, BRANCOS GRANDES</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>16.99</v>
       </c>
     </row>
   </sheetData>
